--- a/Milwaukee_Bucks_2025-26_stats.xlsx
+++ b/Milwaukee_Bucks_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1287,6 +1287,132 @@
       </c>
       <c r="S13" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>29</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13</v>
+      </c>
+      <c r="O14" t="n">
+        <v>25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15</v>
+      </c>
+      <c r="O15" t="n">
+        <v>32</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1300,7 +1426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2154,6 +2280,132 @@
       </c>
       <c r="S13" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>18</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2167,7 +2419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3021,6 +3273,132 @@
       </c>
       <c r="S13" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>10</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3034,7 +3412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3887,6 +4265,132 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3923,7 +4427,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.4</v>
+        <v>32.58333333333334</v>
       </c>
     </row>
     <row r="3">
@@ -3933,7 +4437,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.25</v>
+        <v>16.92857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -3943,7 +4447,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.27272727272727</v>
+        <v>13.53846153846154</v>
       </c>
     </row>
     <row r="5">
@@ -3953,7 +4457,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.41666666666667</v>
+        <v>12.14285714285714</v>
       </c>
     </row>
     <row r="6">
@@ -3963,7 +4467,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.25</v>
+        <v>10.78571428571429</v>
       </c>
     </row>
     <row r="7">
@@ -3973,13 +4477,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>10.07142857142857</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kevin Porter Jr.</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -3989,7 +4493,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Kevin Porter Jr.</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3999,21 +4503,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cole Anthony</t>
+          <t>Bobby Portis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.909090909090908</v>
+        <v>9.642857142857142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bobby Portis</t>
+          <t>Cole Anthony</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.583333333333334</v>
+        <v>9.153846153846153</v>
       </c>
     </row>
     <row r="12">
@@ -4033,27 +4537,27 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Amir Coffey</t>
+          <t>Gary Harris</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5</v>
+        <v>2.571428571428572</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Thanasis Antetokounmpo</t>
+          <t>Amir Coffey</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>1.615384615384615</v>
       </c>
     </row>
     <row r="16">
@@ -4069,11 +4573,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gary Harris</t>
+          <t>Thanasis Antetokounmpo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -4119,7 +4623,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2</v>
+        <v>7.083333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -4129,7 +4633,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.666666666666667</v>
+        <v>5.357142857142857</v>
       </c>
     </row>
     <row r="4">
@@ -4139,7 +4643,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.818181818181818</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -4149,7 +4653,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.333333333333333</v>
+        <v>2.142857142857143</v>
       </c>
     </row>
     <row r="6">
@@ -4169,7 +4673,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1.857142857142857</v>
       </c>
     </row>
     <row r="8">
@@ -4179,7 +4683,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.833333333333333</v>
+        <v>1.714285714285714</v>
       </c>
     </row>
     <row r="9">
@@ -4189,7 +4693,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.545454545454545</v>
+        <v>1.692307692307692</v>
       </c>
     </row>
     <row r="10">
@@ -4199,23 +4703,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.333333333333333</v>
+        <v>1.214285714285714</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Andre Jackson Jr.</t>
+          <t>Taurean Prince</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Andre Jackson Jr.</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4229,7 +4733,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="14">
@@ -4239,13 +4743,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mark Sears</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -4255,11 +4759,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>Mark Sears</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17">
@@ -4315,7 +4819,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.9</v>
+        <v>11.33333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -4325,7 +4829,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.333333333333333</v>
+        <v>6.214285714285714</v>
       </c>
     </row>
     <row r="4">
@@ -4335,7 +4839,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.583333333333333</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
@@ -4345,7 +4849,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.181818181818182</v>
+        <v>4.384615384615385</v>
       </c>
     </row>
     <row r="6">
@@ -4355,7 +4859,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.666666666666667</v>
+        <v>3.785714285714286</v>
       </c>
     </row>
     <row r="7">
@@ -4365,7 +4869,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.363636363636364</v>
+        <v>3.461538461538462</v>
       </c>
     </row>
     <row r="8">
@@ -4375,17 +4879,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.583333333333333</v>
+        <v>2.428571428571428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gary Trent Jr.</t>
+          <t>Jericho Sims</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.833333333333333</v>
+        <v>1.777777777777778</v>
       </c>
     </row>
     <row r="10">
@@ -4401,7 +4905,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jericho Sims</t>
+          <t>Gary Trent Jr.</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4415,7 +4919,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.166666666666667</v>
+        <v>1.076923076923077</v>
       </c>
     </row>
     <row r="13">
@@ -4431,47 +4935,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Andre Jackson Jr.</t>
+          <t>Gary Harris</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gary Harris</t>
+          <t>Andre Jackson Jr.</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mark Sears</t>
+          <t>Thanasis Antetokounmpo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kevin Porter Jr.</t>
+          <t>Mark Sears</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Thanasis Antetokounmpo</t>
+          <t>Kevin Porter Jr.</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -4511,7 +5015,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.916666666666667</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -4521,7 +5025,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.333333333333333</v>
+        <v>2.285714285714286</v>
       </c>
     </row>
     <row r="4">
@@ -4531,7 +5035,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.333333333333333</v>
+        <v>2.285714285714286</v>
       </c>
     </row>
     <row r="5">
@@ -4541,13 +5045,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.083333333333333</v>
+        <v>2.285714285714286</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kevin Porter Jr.</t>
+          <t>Pete Nance</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4557,7 +5061,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pete Nance</t>
+          <t>Kevin Porter Jr.</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4581,17 +5085,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.25</v>
+        <v>1.357142857142857</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mark Sears</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="11">
@@ -4601,47 +5105,47 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>Giannis Antetokounmpo</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Giannis Antetokounmpo</t>
+          <t>Mark Sears</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Amir Coffey</t>
+          <t>Gary Harris</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gary Harris</t>
+          <t>Amir Coffey</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="16">
@@ -4685,7 +5189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4967,6 +5471,48 @@
         <v>211</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>147</v>
+      </c>
+      <c r="D14" t="n">
+        <v>134</v>
+      </c>
+      <c r="E14" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>95</v>
+      </c>
+      <c r="D15" t="n">
+        <v>119</v>
+      </c>
+      <c r="E15" t="n">
+        <v>214</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
